--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -1491,7 +1491,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125667483</v>
+        <v>125666555</v>
       </c>
       <c r="B9" t="n">
         <v>57651</v>
@@ -1522,7 +1522,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493407</v>
+        <v>493270</v>
       </c>
       <c r="R9" t="n">
-        <v>7094143</v>
+        <v>7094164</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack i gammelgran med garnlav.</t>
+          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125666555</v>
+        <v>125683879</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>91238</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,39 +1619,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493270</v>
+        <v>493545</v>
       </c>
       <c r="R10" t="n">
-        <v>7094164</v>
+        <v>7094176</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1678,27 +1676,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
+          <t>På död avbruten granstubbe ca 40 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,6 +1705,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1725,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125683879</v>
+        <v>125667483</v>
       </c>
       <c r="B11" t="n">
-        <v>91238</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,37 +1735,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493545</v>
+        <v>493407</v>
       </c>
       <c r="R11" t="n">
-        <v>7094176</v>
+        <v>7094143</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1793,27 +1794,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På död avbruten granstubbe ca 40 m fr grusvägen.</t>
+          <t>Äldre ringhack i gammelgran med garnlav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,7 +1823,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125667690</v>
       </c>
       <c r="B2" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125689348</v>
+        <v>125683525</v>
       </c>
       <c r="B3" t="n">
         <v>57651</v>
@@ -815,24 +815,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493404</v>
+        <v>493611</v>
       </c>
       <c r="R3" t="n">
-        <v>7094076</v>
+        <v>7094209</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -864,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,12 +871,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125683525</v>
+        <v>125689348</v>
       </c>
       <c r="B4" t="n">
         <v>57651</v>
@@ -935,21 +932,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493611</v>
+        <v>493404</v>
       </c>
       <c r="R4" t="n">
-        <v>7094209</v>
+        <v>7094076</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
         <v>125666987</v>
       </c>
       <c r="B5" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125667551</v>
+        <v>125666667</v>
       </c>
       <c r="B7" t="n">
         <v>57651</v>
@@ -1288,7 +1288,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493416</v>
+        <v>493264</v>
       </c>
       <c r="R7" t="n">
-        <v>7094160</v>
+        <v>7094138</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Mycket färska ringhack av tretå. Rinnande kåda.</t>
+          <t>Äldre ringhack på äldre gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,7 +1374,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125666667</v>
+        <v>125667551</v>
       </c>
       <c r="B8" t="n">
         <v>57651</v>
@@ -1405,7 +1405,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493264</v>
+        <v>493416</v>
       </c>
       <c r="R8" t="n">
-        <v>7094138</v>
+        <v>7094160</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre ringhack på äldre gran.</t>
+          <t>Mycket färska ringhack av tretå. Rinnande kåda.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,7 +1491,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125666555</v>
+        <v>125667483</v>
       </c>
       <c r="B9" t="n">
         <v>57651</v>
@@ -1522,7 +1522,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493270</v>
+        <v>493407</v>
       </c>
       <c r="R9" t="n">
-        <v>7094164</v>
+        <v>7094143</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
+          <t>Äldre ringhack i gammelgran med garnlav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125683879</v>
+        <v>125666555</v>
       </c>
       <c r="B10" t="n">
-        <v>91238</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,37 +1619,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493545</v>
+        <v>493270</v>
       </c>
       <c r="R10" t="n">
-        <v>7094176</v>
+        <v>7094164</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1676,27 +1678,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På död avbruten granstubbe ca 40 m fr grusvägen.</t>
+          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,7 +1707,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1724,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125667483</v>
+        <v>125683879</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>91245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,39 +1736,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493407</v>
+        <v>493545</v>
       </c>
       <c r="R11" t="n">
-        <v>7094143</v>
+        <v>7094176</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1794,27 +1793,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack i gammelgran med garnlav.</t>
+          <t>På död avbruten granstubbe ca 40 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,6 +1822,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>125666380</v>
       </c>
       <c r="B13" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>125683817</v>
       </c>
       <c r="B14" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2308,50 +2308,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125683946</v>
+        <v>125666898</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493609</v>
+        <v>493284</v>
       </c>
       <c r="R16" t="n">
-        <v>7094192</v>
+        <v>7094122</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2378,27 +2378,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran.</t>
+          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,10 +2425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125666898</v>
+        <v>125665862</v>
       </c>
       <c r="B17" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493284</v>
+        <v>493347</v>
       </c>
       <c r="R17" t="n">
-        <v>7094122</v>
+        <v>7094199</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
+          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,50 +2542,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125665862</v>
+        <v>125683946</v>
       </c>
       <c r="B18" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493347</v>
+        <v>493609</v>
       </c>
       <c r="R18" t="n">
-        <v>7094199</v>
+        <v>7094192</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2612,27 +2612,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,7 +2659,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125684993</v>
+        <v>125665967</v>
       </c>
       <c r="B19" t="n">
         <v>57651</v>
@@ -2690,19 +2690,19 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493273</v>
+        <v>493355</v>
       </c>
       <c r="R19" t="n">
-        <v>7093990</v>
+        <v>7094221</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2729,27 +2729,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack nere på granen. Färska ringhack högre upp. 2 m fr bäcken.</t>
+          <t>Äldre ringhack av tretå på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,7 +2776,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125665967</v>
+        <v>125684220</v>
       </c>
       <c r="B20" t="n">
         <v>57651</v>
@@ -2805,21 +2805,24 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493355</v>
+        <v>493495</v>
       </c>
       <c r="R20" t="n">
-        <v>7094221</v>
+        <v>7094188</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2846,27 +2849,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretå på gran.</t>
+          <t>Färska ringhack på stor kjolgran 7 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2893,7 +2896,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125689294</v>
+        <v>125684993</v>
       </c>
       <c r="B21" t="n">
         <v>57651</v>
@@ -2924,19 +2927,19 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493420</v>
+        <v>493273</v>
       </c>
       <c r="R21" t="n">
-        <v>7094057</v>
+        <v>7093990</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2968,7 +2971,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2978,7 +2981,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack nere på granen. Färska ringhack högre upp. 2 m fr bäcken.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3005,7 +3013,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125664781</v>
+        <v>125689294</v>
       </c>
       <c r="B22" t="n">
         <v>57651</v>
@@ -3036,19 +3044,19 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493440</v>
+        <v>493420</v>
       </c>
       <c r="R22" t="n">
-        <v>7094193</v>
+        <v>7094057</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3075,27 +3083,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack av tretå ppå stor gran ca 30 m fr grusvägen.</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3122,7 +3125,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125684220</v>
+        <v>125664781</v>
       </c>
       <c r="B23" t="n">
         <v>57651</v>
@@ -3151,24 +3154,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493495</v>
+        <v>493440</v>
       </c>
       <c r="R23" t="n">
-        <v>7094188</v>
+        <v>7094193</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3195,27 +3195,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack på stor kjolgran 7 m fr grusvägen.</t>
+          <t>Färska och äldre ringhack av tretå ppå stor gran ca 30 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3242,7 +3242,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125686241</v>
+        <v>125684017</v>
       </c>
       <c r="B24" t="n">
         <v>57651</v>
@@ -3275,23 +3275,23 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>strandflyn, Jmt</t>
+          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493197</v>
+        <v>493640</v>
       </c>
       <c r="R24" t="n">
-        <v>7094155</v>
+        <v>7094153</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Svårt med täckning och rätt koordinater men halvvägs ner i branten. Äldre ringhack.</t>
+          <t>Färska ringhack ca 2 m upp på gran 5 m fr myren.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3362,7 +3362,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125684017</v>
+        <v>125686241</v>
       </c>
       <c r="B25" t="n">
         <v>57651</v>
@@ -3395,23 +3395,23 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
+          <t>strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493640</v>
+        <v>493197</v>
       </c>
       <c r="R25" t="n">
-        <v>7094153</v>
+        <v>7094155</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack ca 2 m upp på gran 5 m fr myren.</t>
+          <t>Svårt med täckning och rätt koordinater men halvvägs ner i branten. Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3719,7 +3719,7 @@
         <v>125667340</v>
       </c>
       <c r="B28" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125683525</v>
+        <v>125689348</v>
       </c>
       <c r="B3" t="n">
         <v>57651</v>
@@ -815,21 +815,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493611</v>
+        <v>493404</v>
       </c>
       <c r="R3" t="n">
-        <v>7094209</v>
+        <v>7094076</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -861,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,12 +874,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125689348</v>
+        <v>125683525</v>
       </c>
       <c r="B4" t="n">
         <v>57651</v>
@@ -932,24 +935,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493404</v>
+        <v>493611</v>
       </c>
       <c r="R4" t="n">
-        <v>7094076</v>
+        <v>7094209</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125667483</v>
+        <v>125683879</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>91245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,39 +1502,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493407</v>
+        <v>493545</v>
       </c>
       <c r="R9" t="n">
-        <v>7094143</v>
+        <v>7094176</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1561,27 +1559,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack i gammelgran med garnlav.</t>
+          <t>På död avbruten granstubbe ca 40 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,6 +1588,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1608,7 +1607,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125666555</v>
+        <v>125667483</v>
       </c>
       <c r="B10" t="n">
         <v>57651</v>
@@ -1639,7 +1638,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1648,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493270</v>
+        <v>493407</v>
       </c>
       <c r="R10" t="n">
-        <v>7094164</v>
+        <v>7094143</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1683,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1693,12 +1692,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
+          <t>Äldre ringhack i gammelgran med garnlav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125683879</v>
+        <v>125666555</v>
       </c>
       <c r="B11" t="n">
-        <v>91245</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,37 +1735,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493545</v>
+        <v>493270</v>
       </c>
       <c r="R11" t="n">
-        <v>7094176</v>
+        <v>7094164</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1793,27 +1794,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På död avbruten granstubbe ca 40 m fr grusvägen.</t>
+          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,7 +1823,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -3482,50 +3482,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125684959</v>
+        <v>125667340</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493277</v>
+        <v>493359</v>
       </c>
       <c r="R26" t="n">
-        <v>7093987</v>
+        <v>7094123</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3552,27 +3552,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack på 2 granar bredvid varandra</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3599,7 +3599,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125684059</v>
+        <v>125684959</v>
       </c>
       <c r="B27" t="n">
         <v>57651</v>
@@ -3635,14 +3635,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493628</v>
+        <v>493277</v>
       </c>
       <c r="R27" t="n">
-        <v>7094137</v>
+        <v>7093987</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
+          <t>Äldre ringhack på 2 granar bredvid varandra</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3716,50 +3716,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125667340</v>
+        <v>125684059</v>
       </c>
       <c r="B28" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493359</v>
+        <v>493628</v>
       </c>
       <c r="R28" t="n">
-        <v>7094123</v>
+        <v>7094137</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3786,27 +3786,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125667690</v>
       </c>
       <c r="B2" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,53 +786,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125689348</v>
+        <v>125666987</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>98353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493404</v>
+        <v>493310</v>
       </c>
       <c r="R3" t="n">
-        <v>7094076</v>
+        <v>7094122</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -859,27 +856,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125683525</v>
+        <v>125689348</v>
       </c>
       <c r="B4" t="n">
         <v>57651</v>
@@ -935,21 +932,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493611</v>
+        <v>493404</v>
       </c>
       <c r="R4" t="n">
-        <v>7094209</v>
+        <v>7094076</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,50 +1023,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125666987</v>
+        <v>125683525</v>
       </c>
       <c r="B5" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493310</v>
+        <v>493611</v>
       </c>
       <c r="R5" t="n">
-        <v>7094122</v>
+        <v>7094209</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,27 +1093,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1257,7 +1257,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125666667</v>
+        <v>125667551</v>
       </c>
       <c r="B7" t="n">
         <v>57651</v>
@@ -1288,7 +1288,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493264</v>
+        <v>493416</v>
       </c>
       <c r="R7" t="n">
-        <v>7094138</v>
+        <v>7094160</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre ringhack på äldre gran.</t>
+          <t>Mycket färska ringhack av tretå. Rinnande kåda.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,7 +1374,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125667551</v>
+        <v>125666667</v>
       </c>
       <c r="B8" t="n">
         <v>57651</v>
@@ -1405,7 +1405,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493416</v>
+        <v>493264</v>
       </c>
       <c r="R8" t="n">
-        <v>7094160</v>
+        <v>7094138</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Mycket färska ringhack av tretå. Rinnande kåda.</t>
+          <t>Äldre ringhack på äldre gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,7 +1494,7 @@
         <v>125683879</v>
       </c>
       <c r="B9" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>125666380</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>125683817</v>
       </c>
       <c r="B14" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2308,50 +2308,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125666898</v>
+        <v>125683946</v>
       </c>
       <c r="B16" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493284</v>
+        <v>493609</v>
       </c>
       <c r="R16" t="n">
-        <v>7094122</v>
+        <v>7094192</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2378,27 +2378,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,10 +2425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125665862</v>
+        <v>125666898</v>
       </c>
       <c r="B17" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493347</v>
+        <v>493284</v>
       </c>
       <c r="R17" t="n">
-        <v>7094199</v>
+        <v>7094122</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
+          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,50 +2542,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125683946</v>
+        <v>125665862</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>98353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493609</v>
+        <v>493347</v>
       </c>
       <c r="R18" t="n">
-        <v>7094192</v>
+        <v>7094199</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2612,27 +2612,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran.</t>
+          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,7 +2659,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125665967</v>
+        <v>125684993</v>
       </c>
       <c r="B19" t="n">
         <v>57651</v>
@@ -2690,19 +2690,19 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493355</v>
+        <v>493273</v>
       </c>
       <c r="R19" t="n">
-        <v>7094221</v>
+        <v>7093990</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2729,27 +2729,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretå på gran.</t>
+          <t>Äldre ringhack nere på granen. Färska ringhack högre upp. 2 m fr bäcken.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,7 +2776,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125684220</v>
+        <v>125665967</v>
       </c>
       <c r="B20" t="n">
         <v>57651</v>
@@ -2805,24 +2805,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493495</v>
+        <v>493355</v>
       </c>
       <c r="R20" t="n">
-        <v>7094188</v>
+        <v>7094221</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2849,27 +2846,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack på stor kjolgran 7 m fr grusvägen.</t>
+          <t>Äldre ringhack av tretå på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2896,7 +2893,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125684993</v>
+        <v>125689294</v>
       </c>
       <c r="B21" t="n">
         <v>57651</v>
@@ -2927,19 +2924,19 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493273</v>
+        <v>493420</v>
       </c>
       <c r="R21" t="n">
-        <v>7093990</v>
+        <v>7094057</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2971,7 +2968,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2981,12 +2978,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack nere på granen. Färska ringhack högre upp. 2 m fr bäcken.</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,7 +3005,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125689294</v>
+        <v>125664781</v>
       </c>
       <c r="B22" t="n">
         <v>57651</v>
@@ -3044,19 +3036,19 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493420</v>
+        <v>493440</v>
       </c>
       <c r="R22" t="n">
-        <v>7094057</v>
+        <v>7094193</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3083,22 +3075,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack av tretå ppå stor gran ca 30 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3125,7 +3122,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125664781</v>
+        <v>125684220</v>
       </c>
       <c r="B23" t="n">
         <v>57651</v>
@@ -3154,21 +3151,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493440</v>
+        <v>493495</v>
       </c>
       <c r="R23" t="n">
-        <v>7094193</v>
+        <v>7094188</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3195,27 +3195,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack av tretå ppå stor gran ca 30 m fr grusvägen.</t>
+          <t>Färska ringhack på stor kjolgran 7 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3242,7 +3242,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125684017</v>
+        <v>125686241</v>
       </c>
       <c r="B24" t="n">
         <v>57651</v>
@@ -3275,23 +3275,23 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
+          <t>strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493640</v>
+        <v>493197</v>
       </c>
       <c r="R24" t="n">
-        <v>7094153</v>
+        <v>7094155</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack ca 2 m upp på gran 5 m fr myren.</t>
+          <t>Svårt med täckning och rätt koordinater men halvvägs ner i branten. Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3362,7 +3362,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125686241</v>
+        <v>125684017</v>
       </c>
       <c r="B25" t="n">
         <v>57651</v>
@@ -3395,23 +3395,23 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>strandflyn, Jmt</t>
+          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493197</v>
+        <v>493640</v>
       </c>
       <c r="R25" t="n">
-        <v>7094155</v>
+        <v>7094153</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Svårt med täckning och rätt koordinater men halvvägs ner i branten. Äldre ringhack.</t>
+          <t>Färska ringhack ca 2 m upp på gran 5 m fr myren.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3482,50 +3482,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125667340</v>
+        <v>125684959</v>
       </c>
       <c r="B26" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493359</v>
+        <v>493277</v>
       </c>
       <c r="R26" t="n">
-        <v>7094123</v>
+        <v>7093987</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3552,27 +3552,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Äldre ringhack på 2 granar bredvid varandra</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3599,7 +3599,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125684959</v>
+        <v>125684059</v>
       </c>
       <c r="B27" t="n">
         <v>57651</v>
@@ -3635,14 +3635,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Jmt</t>
+          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493277</v>
+        <v>493628</v>
       </c>
       <c r="R27" t="n">
-        <v>7093987</v>
+        <v>7094137</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på 2 granar bredvid varandra</t>
+          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3716,50 +3716,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125684059</v>
+        <v>125667340</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>98353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493628</v>
+        <v>493359</v>
       </c>
       <c r="R28" t="n">
-        <v>7094137</v>
+        <v>7094123</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3786,27 +3786,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>125666987</v>
       </c>
       <c r="B3" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>125666380</v>
       </c>
       <c r="B13" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2308,50 +2308,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125683946</v>
+        <v>125666898</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>98355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493609</v>
+        <v>493284</v>
       </c>
       <c r="R16" t="n">
-        <v>7094192</v>
+        <v>7094122</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2378,27 +2378,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran.</t>
+          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,10 +2425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125666898</v>
+        <v>125665862</v>
       </c>
       <c r="B17" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493284</v>
+        <v>493347</v>
       </c>
       <c r="R17" t="n">
-        <v>7094122</v>
+        <v>7094199</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
+          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,50 +2542,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125665862</v>
+        <v>125683946</v>
       </c>
       <c r="B18" t="n">
-        <v>98353</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493347</v>
+        <v>493609</v>
       </c>
       <c r="R18" t="n">
-        <v>7094199</v>
+        <v>7094192</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2612,27 +2612,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3719,7 +3719,7 @@
         <v>125667340</v>
       </c>
       <c r="B28" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125683817</v>
+        <v>125667284</v>
       </c>
       <c r="B14" t="n">
-        <v>91228</v>
+        <v>57651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,37 +2086,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493580</v>
+        <v>493342</v>
       </c>
       <c r="R14" t="n">
-        <v>7094211</v>
+        <v>7094110</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2143,27 +2145,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På nedbruten granlåga. 30 m fr vägen.</t>
+          <t>Äldre ringhack av tretå på grov gran med garnlav i.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,7 +2174,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2191,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125667284</v>
+        <v>125683817</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>91228</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,39 +2203,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493342</v>
+        <v>493580</v>
       </c>
       <c r="R15" t="n">
-        <v>7094110</v>
+        <v>7094211</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2261,27 +2260,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretå på grov gran med garnlav i.</t>
+          <t>På nedbruten granlåga. 30 m fr vägen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,6 +2289,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2308,50 +2308,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125666898</v>
+        <v>125683946</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493284</v>
+        <v>493609</v>
       </c>
       <c r="R16" t="n">
-        <v>7094122</v>
+        <v>7094192</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2378,27 +2378,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,7 +2425,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125665862</v>
+        <v>125666898</v>
       </c>
       <c r="B17" t="n">
         <v>98355</v>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493347</v>
+        <v>493284</v>
       </c>
       <c r="R17" t="n">
-        <v>7094199</v>
+        <v>7094122</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
+          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,50 +2542,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125683946</v>
+        <v>125665862</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>98355</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493609</v>
+        <v>493347</v>
       </c>
       <c r="R18" t="n">
-        <v>7094192</v>
+        <v>7094199</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2612,27 +2612,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran.</t>
+          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125667690</v>
       </c>
       <c r="B2" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,50 +786,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125666987</v>
+        <v>125689348</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493310</v>
+        <v>493404</v>
       </c>
       <c r="R3" t="n">
-        <v>7094122</v>
+        <v>7094076</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -856,27 +859,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125689348</v>
+        <v>125683525</v>
       </c>
       <c r="B4" t="n">
         <v>57651</v>
@@ -932,24 +935,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493404</v>
+        <v>493611</v>
       </c>
       <c r="R4" t="n">
-        <v>7094076</v>
+        <v>7094209</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,50 +1023,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125683525</v>
+        <v>125666987</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493611</v>
+        <v>493310</v>
       </c>
       <c r="R5" t="n">
-        <v>7094209</v>
+        <v>7094122</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,27 +1093,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125683879</v>
+        <v>125667483</v>
       </c>
       <c r="B9" t="n">
-        <v>91246</v>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,37 +1502,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493545</v>
+        <v>493407</v>
       </c>
       <c r="R9" t="n">
-        <v>7094176</v>
+        <v>7094143</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1559,27 +1561,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På död avbruten granstubbe ca 40 m fr grusvägen.</t>
+          <t>Äldre ringhack i gammelgran med garnlav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,7 +1590,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1607,7 +1608,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125667483</v>
+        <v>125666555</v>
       </c>
       <c r="B10" t="n">
         <v>57651</v>
@@ -1638,7 +1639,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1647,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493407</v>
+        <v>493270</v>
       </c>
       <c r="R10" t="n">
-        <v>7094143</v>
+        <v>7094164</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1682,7 +1683,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,12 +1693,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack i gammelgran med garnlav.</t>
+          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125666555</v>
+        <v>125683879</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,39 +1736,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493270</v>
+        <v>493545</v>
       </c>
       <c r="R11" t="n">
-        <v>7094164</v>
+        <v>7094176</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1794,27 +1793,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
+          <t>På död avbruten granstubbe ca 40 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,6 +1822,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>125666380</v>
       </c>
       <c r="B13" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>125683817</v>
       </c>
       <c r="B15" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2308,50 +2308,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125683946</v>
+        <v>125666898</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493609</v>
+        <v>493284</v>
       </c>
       <c r="R16" t="n">
-        <v>7094192</v>
+        <v>7094122</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2378,27 +2378,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran.</t>
+          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,10 +2425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125666898</v>
+        <v>125665862</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493284</v>
+        <v>493347</v>
       </c>
       <c r="R17" t="n">
-        <v>7094122</v>
+        <v>7094199</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
+          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,50 +2542,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125665862</v>
+        <v>125683946</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493347</v>
+        <v>493609</v>
       </c>
       <c r="R18" t="n">
-        <v>7094199</v>
+        <v>7094192</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2612,27 +2612,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3719,7 +3719,7 @@
         <v>125667340</v>
       </c>
       <c r="B28" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -786,53 +786,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125689348</v>
+        <v>125666987</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493404</v>
+        <v>493310</v>
       </c>
       <c r="R3" t="n">
-        <v>7094076</v>
+        <v>7094122</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -859,27 +856,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125683525</v>
+        <v>125689348</v>
       </c>
       <c r="B4" t="n">
         <v>57651</v>
@@ -935,21 +932,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493611</v>
+        <v>493404</v>
       </c>
       <c r="R4" t="n">
-        <v>7094209</v>
+        <v>7094076</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,50 +1023,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125666987</v>
+        <v>125683525</v>
       </c>
       <c r="B5" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493310</v>
+        <v>493611</v>
       </c>
       <c r="R5" t="n">
-        <v>7094122</v>
+        <v>7094209</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,27 +1093,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1961,7 +1961,7 @@
         <v>125666380</v>
       </c>
       <c r="B13" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125667284</v>
+        <v>125683817</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,39 +2086,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493342</v>
+        <v>493580</v>
       </c>
       <c r="R14" t="n">
-        <v>7094110</v>
+        <v>7094211</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2145,27 +2143,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretå på grov gran med garnlav i.</t>
+          <t>På nedbruten granlåga. 30 m fr vägen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,6 +2172,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2192,10 +2191,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125683817</v>
+        <v>125667284</v>
       </c>
       <c r="B15" t="n">
-        <v>91232</v>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2203,37 +2202,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493580</v>
+        <v>493342</v>
       </c>
       <c r="R15" t="n">
-        <v>7094211</v>
+        <v>7094110</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2260,27 +2261,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På nedbruten granlåga. 30 m fr vägen.</t>
+          <t>Äldre ringhack av tretå på grov gran med garnlav i.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,7 +2290,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2308,50 +2308,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125666898</v>
+        <v>125683946</v>
       </c>
       <c r="B16" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493284</v>
+        <v>493609</v>
       </c>
       <c r="R16" t="n">
-        <v>7094122</v>
+        <v>7094192</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2378,27 +2378,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2428,7 +2428,7 @@
         <v>125665862</v>
       </c>
       <c r="B17" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,50 +2542,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125683946</v>
+        <v>125666898</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493609</v>
+        <v>493284</v>
       </c>
       <c r="R18" t="n">
-        <v>7094192</v>
+        <v>7094122</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2612,27 +2612,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran.</t>
+          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3482,50 +3482,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125684959</v>
+        <v>125667340</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493277</v>
+        <v>493359</v>
       </c>
       <c r="R26" t="n">
-        <v>7093987</v>
+        <v>7094123</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3552,27 +3552,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack på 2 granar bredvid varandra</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3599,7 +3599,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125684059</v>
+        <v>125684959</v>
       </c>
       <c r="B27" t="n">
         <v>57651</v>
@@ -3635,14 +3635,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493628</v>
+        <v>493277</v>
       </c>
       <c r="R27" t="n">
-        <v>7094137</v>
+        <v>7093987</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
+          <t>Äldre ringhack på 2 granar bredvid varandra</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3716,50 +3716,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125667340</v>
+        <v>125684059</v>
       </c>
       <c r="B28" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493359</v>
+        <v>493628</v>
       </c>
       <c r="R28" t="n">
-        <v>7094123</v>
+        <v>7094137</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3786,27 +3786,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -3482,50 +3482,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125667340</v>
+        <v>125684959</v>
       </c>
       <c r="B26" t="n">
-        <v>98360</v>
+        <v>57651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493359</v>
+        <v>493277</v>
       </c>
       <c r="R26" t="n">
-        <v>7094123</v>
+        <v>7093987</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3552,27 +3552,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Äldre ringhack på 2 granar bredvid varandra</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3599,7 +3599,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125684959</v>
+        <v>125684059</v>
       </c>
       <c r="B27" t="n">
         <v>57651</v>
@@ -3635,14 +3635,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Jmt</t>
+          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493277</v>
+        <v>493628</v>
       </c>
       <c r="R27" t="n">
-        <v>7093987</v>
+        <v>7094137</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på 2 granar bredvid varandra</t>
+          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3716,50 +3716,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125684059</v>
+        <v>125667340</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493628</v>
+        <v>493359</v>
       </c>
       <c r="R28" t="n">
-        <v>7094137</v>
+        <v>7094123</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3786,27 +3786,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125667690</v>
       </c>
       <c r="B2" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>125666987</v>
       </c>
       <c r="B3" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>125689348</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>125683525</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>125667149</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125667551</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>125666667</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125667483</v>
+        <v>125683879</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>91252</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,39 +1502,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493407</v>
+        <v>493545</v>
       </c>
       <c r="R9" t="n">
-        <v>7094143</v>
+        <v>7094176</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1561,27 +1559,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack i gammelgran med garnlav.</t>
+          <t>På död avbruten granstubbe ca 40 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,6 +1588,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1608,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125666555</v>
+        <v>125667483</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1638,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1648,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493270</v>
+        <v>493407</v>
       </c>
       <c r="R10" t="n">
-        <v>7094164</v>
+        <v>7094143</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1683,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1693,12 +1692,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
+          <t>Äldre ringhack i gammelgran med garnlav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125683879</v>
+        <v>125666555</v>
       </c>
       <c r="B11" t="n">
-        <v>91250</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,37 +1735,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493545</v>
+        <v>493270</v>
       </c>
       <c r="R11" t="n">
-        <v>7094176</v>
+        <v>7094164</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1793,27 +1794,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På död avbruten granstubbe ca 40 m fr grusvägen.</t>
+          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,7 +1823,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>125665004</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>125666380</v>
       </c>
       <c r="B13" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>125683817</v>
       </c>
       <c r="B14" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>125667284</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>125683946</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125665862</v>
+        <v>125666898</v>
       </c>
       <c r="B17" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493347</v>
+        <v>493284</v>
       </c>
       <c r="R17" t="n">
-        <v>7094199</v>
+        <v>7094122</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
+          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,10 +2542,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125666898</v>
+        <v>125665862</v>
       </c>
       <c r="B18" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493284</v>
+        <v>493347</v>
       </c>
       <c r="R18" t="n">
-        <v>7094122</v>
+        <v>7094199</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
+          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2662,7 +2662,7 @@
         <v>125684993</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>125665967</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>125689294</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>125664781</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>125684220</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>125686241</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>125684017</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>125684959</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>125684059</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>125667340</v>
       </c>
       <c r="B28" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>125667230</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -2308,50 +2308,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125683946</v>
+        <v>125666898</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>98362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493609</v>
+        <v>493284</v>
       </c>
       <c r="R16" t="n">
-        <v>7094192</v>
+        <v>7094122</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2378,27 +2378,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran.</t>
+          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,7 +2425,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125666898</v>
+        <v>125665862</v>
       </c>
       <c r="B17" t="n">
         <v>98362</v>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493284</v>
+        <v>493347</v>
       </c>
       <c r="R17" t="n">
-        <v>7094122</v>
+        <v>7094199</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
+          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,50 +2542,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125665862</v>
+        <v>125683946</v>
       </c>
       <c r="B18" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493347</v>
+        <v>493609</v>
       </c>
       <c r="R18" t="n">
-        <v>7094199</v>
+        <v>7094192</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2612,27 +2612,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125667690</v>
       </c>
       <c r="B2" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,50 +786,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125666987</v>
+        <v>125689348</v>
       </c>
       <c r="B3" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493310</v>
+        <v>493404</v>
       </c>
       <c r="R3" t="n">
-        <v>7094122</v>
+        <v>7094076</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -856,27 +859,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125689348</v>
+        <v>125683525</v>
       </c>
       <c r="B4" t="n">
         <v>57652</v>
@@ -932,24 +935,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493404</v>
+        <v>493611</v>
       </c>
       <c r="R4" t="n">
-        <v>7094076</v>
+        <v>7094209</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,50 +1023,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125683525</v>
+        <v>125666987</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>98364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493611</v>
+        <v>493310</v>
       </c>
       <c r="R5" t="n">
-        <v>7094209</v>
+        <v>7094122</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,27 +1093,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125683879</v>
+        <v>125667483</v>
       </c>
       <c r="B9" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,37 +1502,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493545</v>
+        <v>493407</v>
       </c>
       <c r="R9" t="n">
-        <v>7094176</v>
+        <v>7094143</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1559,27 +1561,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På död avbruten granstubbe ca 40 m fr grusvägen.</t>
+          <t>Äldre ringhack i gammelgran med garnlav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,7 +1590,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1607,7 +1608,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125667483</v>
+        <v>125666555</v>
       </c>
       <c r="B10" t="n">
         <v>57652</v>
@@ -1638,7 +1639,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1647,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493407</v>
+        <v>493270</v>
       </c>
       <c r="R10" t="n">
-        <v>7094143</v>
+        <v>7094164</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1682,7 +1683,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,12 +1693,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack i gammelgran med garnlav.</t>
+          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125666555</v>
+        <v>125683879</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>91254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,39 +1736,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493270</v>
+        <v>493545</v>
       </c>
       <c r="R11" t="n">
-        <v>7094164</v>
+        <v>7094176</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1794,27 +1793,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
+          <t>På död avbruten granstubbe ca 40 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,6 +1822,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>125666380</v>
       </c>
       <c r="B13" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125683817</v>
+        <v>125667284</v>
       </c>
       <c r="B14" t="n">
-        <v>91234</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,37 +2086,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493580</v>
+        <v>493342</v>
       </c>
       <c r="R14" t="n">
-        <v>7094211</v>
+        <v>7094110</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2143,27 +2145,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På nedbruten granlåga. 30 m fr vägen.</t>
+          <t>Äldre ringhack av tretå på grov gran med garnlav i.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,7 +2174,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2191,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125667284</v>
+        <v>125683817</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>91236</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,39 +2203,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493342</v>
+        <v>493580</v>
       </c>
       <c r="R15" t="n">
-        <v>7094110</v>
+        <v>7094211</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2261,27 +2260,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretå på grov gran med garnlav i.</t>
+          <t>På nedbruten granlåga. 30 m fr vägen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,6 +2289,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2308,50 +2308,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125666898</v>
+        <v>125683946</v>
       </c>
       <c r="B16" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493284</v>
+        <v>493609</v>
       </c>
       <c r="R16" t="n">
-        <v>7094122</v>
+        <v>7094192</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2378,27 +2378,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,10 +2425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125665862</v>
+        <v>125666898</v>
       </c>
       <c r="B17" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493347</v>
+        <v>493284</v>
       </c>
       <c r="R17" t="n">
-        <v>7094199</v>
+        <v>7094122</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
+          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,50 +2542,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125683946</v>
+        <v>125665862</v>
       </c>
       <c r="B18" t="n">
-        <v>57652</v>
+        <v>98364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493609</v>
+        <v>493347</v>
       </c>
       <c r="R18" t="n">
-        <v>7094192</v>
+        <v>7094199</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2612,27 +2612,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran.</t>
+          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3719,7 +3719,7 @@
         <v>125667340</v>
       </c>
       <c r="B28" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125667690</v>
       </c>
       <c r="B2" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,53 +786,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125689348</v>
+        <v>125666987</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>98366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493404</v>
+        <v>493310</v>
       </c>
       <c r="R3" t="n">
-        <v>7094076</v>
+        <v>7094122</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -859,27 +856,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125683525</v>
+        <v>125689348</v>
       </c>
       <c r="B4" t="n">
         <v>57652</v>
@@ -935,21 +932,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493611</v>
+        <v>493404</v>
       </c>
       <c r="R4" t="n">
-        <v>7094209</v>
+        <v>7094076</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,50 +1023,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125666987</v>
+        <v>125683525</v>
       </c>
       <c r="B5" t="n">
-        <v>98364</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493310</v>
+        <v>493611</v>
       </c>
       <c r="R5" t="n">
-        <v>7094122</v>
+        <v>7094209</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,27 +1093,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1728,7 +1728,7 @@
         <v>125683879</v>
       </c>
       <c r="B11" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>125666380</v>
       </c>
       <c r="B13" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125667284</v>
+        <v>125683817</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>91238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,39 +2086,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493342</v>
+        <v>493580</v>
       </c>
       <c r="R14" t="n">
-        <v>7094110</v>
+        <v>7094211</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2145,27 +2143,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretå på grov gran med garnlav i.</t>
+          <t>På nedbruten granlåga. 30 m fr vägen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,6 +2172,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2192,10 +2191,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125683817</v>
+        <v>125667284</v>
       </c>
       <c r="B15" t="n">
-        <v>91236</v>
+        <v>57652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2203,37 +2202,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493580</v>
+        <v>493342</v>
       </c>
       <c r="R15" t="n">
-        <v>7094211</v>
+        <v>7094110</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2260,27 +2261,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På nedbruten granlåga. 30 m fr vägen.</t>
+          <t>Äldre ringhack av tretå på grov gran med garnlav i.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,7 +2290,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>125666898</v>
       </c>
       <c r="B17" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>125665862</v>
       </c>
       <c r="B18" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>125667340</v>
       </c>
       <c r="B28" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -786,50 +786,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125666987</v>
+        <v>125689348</v>
       </c>
       <c r="B3" t="n">
-        <v>98366</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493310</v>
+        <v>493404</v>
       </c>
       <c r="R3" t="n">
-        <v>7094122</v>
+        <v>7094076</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -856,27 +859,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125689348</v>
+        <v>125683525</v>
       </c>
       <c r="B4" t="n">
         <v>57652</v>
@@ -932,24 +935,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493404</v>
+        <v>493611</v>
       </c>
       <c r="R4" t="n">
-        <v>7094076</v>
+        <v>7094209</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,50 +1023,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125683525</v>
+        <v>125666987</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>98366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493611</v>
+        <v>493310</v>
       </c>
       <c r="R5" t="n">
-        <v>7094209</v>
+        <v>7094122</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,27 +1093,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -3482,50 +3482,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125684959</v>
+        <v>125667340</v>
       </c>
       <c r="B26" t="n">
-        <v>57652</v>
+        <v>98366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493277</v>
+        <v>493359</v>
       </c>
       <c r="R26" t="n">
-        <v>7093987</v>
+        <v>7094123</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3552,27 +3552,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack på 2 granar bredvid varandra</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3599,7 +3599,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125684059</v>
+        <v>125684959</v>
       </c>
       <c r="B27" t="n">
         <v>57652</v>
@@ -3635,14 +3635,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493628</v>
+        <v>493277</v>
       </c>
       <c r="R27" t="n">
-        <v>7094137</v>
+        <v>7093987</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
+          <t>Äldre ringhack på 2 granar bredvid varandra</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3716,50 +3716,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125667340</v>
+        <v>125684059</v>
       </c>
       <c r="B28" t="n">
-        <v>98366</v>
+        <v>57652</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493359</v>
+        <v>493628</v>
       </c>
       <c r="R28" t="n">
-        <v>7094123</v>
+        <v>7094137</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3786,27 +3786,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125667690</v>
       </c>
       <c r="B2" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,53 +786,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125689348</v>
+        <v>125666987</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>98370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493404</v>
+        <v>493310</v>
       </c>
       <c r="R3" t="n">
-        <v>7094076</v>
+        <v>7094122</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -859,27 +856,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125683525</v>
+        <v>125689348</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,21 +932,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493611</v>
+        <v>493404</v>
       </c>
       <c r="R4" t="n">
-        <v>7094209</v>
+        <v>7094076</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,50 +1023,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125666987</v>
+        <v>125683525</v>
       </c>
       <c r="B5" t="n">
-        <v>98366</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493310</v>
+        <v>493611</v>
       </c>
       <c r="R5" t="n">
-        <v>7094122</v>
+        <v>7094209</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,27 +1093,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1143,7 @@
         <v>125667149</v>
       </c>
       <c r="B6" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125667551</v>
+        <v>125666667</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493416</v>
+        <v>493264</v>
       </c>
       <c r="R7" t="n">
-        <v>7094160</v>
+        <v>7094138</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Mycket färska ringhack av tretå. Rinnande kåda.</t>
+          <t>Äldre ringhack på äldre gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125666667</v>
+        <v>125667551</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493264</v>
+        <v>493416</v>
       </c>
       <c r="R8" t="n">
-        <v>7094138</v>
+        <v>7094160</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre ringhack på äldre gran.</t>
+          <t>Mycket färska ringhack av tretå. Rinnande kåda.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125667483</v>
+        <v>125683879</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>91260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,39 +1502,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493407</v>
+        <v>493545</v>
       </c>
       <c r="R9" t="n">
-        <v>7094143</v>
+        <v>7094176</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1561,27 +1559,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack i gammelgran med garnlav.</t>
+          <t>På död avbruten granstubbe ca 40 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,6 +1588,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1611,7 +1610,7 @@
         <v>125666555</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,10 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125683879</v>
+        <v>125667483</v>
       </c>
       <c r="B11" t="n">
-        <v>91256</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,37 +1735,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493545</v>
+        <v>493407</v>
       </c>
       <c r="R11" t="n">
-        <v>7094176</v>
+        <v>7094143</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1793,27 +1794,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På död avbruten granstubbe ca 40 m fr grusvägen.</t>
+          <t>Äldre ringhack i gammelgran med garnlav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,7 +1823,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>125665004</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>125666380</v>
       </c>
       <c r="B13" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>125683817</v>
       </c>
       <c r="B14" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>125667284</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2308,50 +2308,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125683946</v>
+        <v>125666898</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>98370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493609</v>
+        <v>493284</v>
       </c>
       <c r="R16" t="n">
-        <v>7094192</v>
+        <v>7094122</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2378,27 +2378,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran.</t>
+          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,10 +2425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125666898</v>
+        <v>125665862</v>
       </c>
       <c r="B17" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493284</v>
+        <v>493347</v>
       </c>
       <c r="R17" t="n">
-        <v>7094122</v>
+        <v>7094199</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
+          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,50 +2542,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125665862</v>
+        <v>125683946</v>
       </c>
       <c r="B18" t="n">
-        <v>98366</v>
+        <v>57656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493347</v>
+        <v>493609</v>
       </c>
       <c r="R18" t="n">
-        <v>7094199</v>
+        <v>7094192</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2612,27 +2612,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2662,7 +2662,7 @@
         <v>125684993</v>
       </c>
       <c r="B19" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>125665967</v>
       </c>
       <c r="B20" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>125689294</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>125664781</v>
       </c>
       <c r="B22" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>125684220</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>125686241</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>125684017</v>
       </c>
       <c r="B25" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3482,50 +3482,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125667340</v>
+        <v>125684959</v>
       </c>
       <c r="B26" t="n">
-        <v>98366</v>
+        <v>57656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493359</v>
+        <v>493277</v>
       </c>
       <c r="R26" t="n">
-        <v>7094123</v>
+        <v>7093987</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3552,27 +3552,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Äldre ringhack på 2 granar bredvid varandra</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3599,10 +3599,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125684959</v>
+        <v>125684059</v>
       </c>
       <c r="B27" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,14 +3635,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Jmt</t>
+          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493277</v>
+        <v>493628</v>
       </c>
       <c r="R27" t="n">
-        <v>7093987</v>
+        <v>7094137</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på 2 granar bredvid varandra</t>
+          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3716,50 +3716,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125684059</v>
+        <v>125667340</v>
       </c>
       <c r="B28" t="n">
-        <v>57652</v>
+        <v>98370</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493628</v>
+        <v>493359</v>
       </c>
       <c r="R28" t="n">
-        <v>7094137</v>
+        <v>7094123</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3786,27 +3786,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3836,7 +3836,7 @@
         <v>125667230</v>
       </c>
       <c r="B29" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -1257,7 +1257,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125666667</v>
+        <v>125667551</v>
       </c>
       <c r="B7" t="n">
         <v>57656</v>
@@ -1288,7 +1288,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493264</v>
+        <v>493416</v>
       </c>
       <c r="R7" t="n">
-        <v>7094138</v>
+        <v>7094160</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre ringhack på äldre gran.</t>
+          <t>Mycket färska ringhack av tretå. Rinnande kåda.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,7 +1374,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125667551</v>
+        <v>125666667</v>
       </c>
       <c r="B8" t="n">
         <v>57656</v>
@@ -1405,7 +1405,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493416</v>
+        <v>493264</v>
       </c>
       <c r="R8" t="n">
-        <v>7094160</v>
+        <v>7094138</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Mycket färska ringhack av tretå. Rinnande kåda.</t>
+          <t>Äldre ringhack på äldre gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -786,50 +786,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125666987</v>
+        <v>125683525</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493310</v>
+        <v>493611</v>
       </c>
       <c r="R3" t="n">
-        <v>7094122</v>
+        <v>7094209</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -856,27 +856,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,53 +903,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125689348</v>
+        <v>125666987</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493404</v>
+        <v>493310</v>
       </c>
       <c r="R4" t="n">
-        <v>7094076</v>
+        <v>7094122</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -976,27 +973,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125683525</v>
+        <v>125689348</v>
       </c>
       <c r="B5" t="n">
         <v>57656</v>
@@ -1052,21 +1049,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493611</v>
+        <v>493404</v>
       </c>
       <c r="R5" t="n">
-        <v>7094209</v>
+        <v>7094076</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1607,7 +1607,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125666555</v>
+        <v>125667483</v>
       </c>
       <c r="B10" t="n">
         <v>57656</v>
@@ -1638,7 +1638,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493270</v>
+        <v>493407</v>
       </c>
       <c r="R10" t="n">
-        <v>7094164</v>
+        <v>7094143</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
+          <t>Äldre ringhack i gammelgran med garnlav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,7 +1724,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125667483</v>
+        <v>125666555</v>
       </c>
       <c r="B11" t="n">
         <v>57656</v>
@@ -1755,7 +1755,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493407</v>
+        <v>493270</v>
       </c>
       <c r="R11" t="n">
-        <v>7094143</v>
+        <v>7094164</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack i gammelgran med garnlav.</t>
+          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1961,7 +1961,7 @@
         <v>125666380</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>125666898</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>125665862</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125684993</v>
+        <v>125665967</v>
       </c>
       <c r="B19" t="n">
         <v>57656</v>
@@ -2690,19 +2690,19 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493273</v>
+        <v>493355</v>
       </c>
       <c r="R19" t="n">
-        <v>7093990</v>
+        <v>7094221</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2729,27 +2729,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack nere på granen. Färska ringhack högre upp. 2 m fr bäcken.</t>
+          <t>Äldre ringhack av tretå på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,7 +2776,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125665967</v>
+        <v>125684993</v>
       </c>
       <c r="B20" t="n">
         <v>57656</v>
@@ -2807,19 +2807,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493355</v>
+        <v>493273</v>
       </c>
       <c r="R20" t="n">
-        <v>7094221</v>
+        <v>7093990</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2846,27 +2846,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretå på gran.</t>
+          <t>Äldre ringhack nere på granen. Färska ringhack högre upp. 2 m fr bäcken.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3719,7 +3719,7 @@
         <v>125667340</v>
       </c>
       <c r="B28" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125683525</v>
+        <v>125689348</v>
       </c>
       <c r="B3" t="n">
         <v>57656</v>
@@ -815,21 +815,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493611</v>
+        <v>493404</v>
       </c>
       <c r="R3" t="n">
-        <v>7094209</v>
+        <v>7094076</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -861,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,12 +874,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,50 +906,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125666987</v>
+        <v>125683525</v>
       </c>
       <c r="B4" t="n">
-        <v>98373</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493310</v>
+        <v>493611</v>
       </c>
       <c r="R4" t="n">
-        <v>7094122</v>
+        <v>7094209</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -973,27 +976,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,53 +1023,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125689348</v>
+        <v>125666987</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493404</v>
+        <v>493310</v>
       </c>
       <c r="R5" t="n">
-        <v>7094076</v>
+        <v>7094122</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,27 +1093,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125683817</v>
+        <v>125667284</v>
       </c>
       <c r="B14" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,37 +2086,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493580</v>
+        <v>493342</v>
       </c>
       <c r="R14" t="n">
-        <v>7094211</v>
+        <v>7094110</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2143,27 +2145,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På nedbruten granlåga. 30 m fr vägen.</t>
+          <t>Äldre ringhack av tretå på grov gran med garnlav i.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,7 +2174,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2191,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125667284</v>
+        <v>125683817</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>91242</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2202,39 +2203,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493342</v>
+        <v>493580</v>
       </c>
       <c r="R15" t="n">
-        <v>7094110</v>
+        <v>7094211</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2261,27 +2260,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretå på grov gran med garnlav i.</t>
+          <t>På nedbruten granlåga. 30 m fr vägen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,6 +2289,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2659,7 +2659,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125665967</v>
+        <v>125684220</v>
       </c>
       <c r="B19" t="n">
         <v>57656</v>
@@ -2688,21 +2688,24 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493355</v>
+        <v>493495</v>
       </c>
       <c r="R19" t="n">
-        <v>7094221</v>
+        <v>7094188</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2729,27 +2732,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretå på gran.</t>
+          <t>Färska ringhack på stor kjolgran 7 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,7 +2779,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125684993</v>
+        <v>125665967</v>
       </c>
       <c r="B20" t="n">
         <v>57656</v>
@@ -2807,19 +2810,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493273</v>
+        <v>493355</v>
       </c>
       <c r="R20" t="n">
-        <v>7093990</v>
+        <v>7094221</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2846,27 +2849,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack nere på granen. Färska ringhack högre upp. 2 m fr bäcken.</t>
+          <t>Äldre ringhack av tretå på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2893,7 +2896,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125689294</v>
+        <v>125664781</v>
       </c>
       <c r="B21" t="n">
         <v>57656</v>
@@ -2924,19 +2927,19 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493420</v>
+        <v>493440</v>
       </c>
       <c r="R21" t="n">
-        <v>7094057</v>
+        <v>7094193</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2963,22 +2966,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack av tretå ppå stor gran ca 30 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3005,7 +3013,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125664781</v>
+        <v>125684993</v>
       </c>
       <c r="B22" t="n">
         <v>57656</v>
@@ -3041,14 +3049,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493440</v>
+        <v>493273</v>
       </c>
       <c r="R22" t="n">
-        <v>7094193</v>
+        <v>7093990</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3075,27 +3083,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack av tretå ppå stor gran ca 30 m fr grusvägen.</t>
+          <t>Äldre ringhack nere på granen. Färska ringhack högre upp. 2 m fr bäcken.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3122,7 +3130,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125684220</v>
+        <v>125689294</v>
       </c>
       <c r="B23" t="n">
         <v>57656</v>
@@ -3151,24 +3159,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493495</v>
+        <v>493420</v>
       </c>
       <c r="R23" t="n">
-        <v>7094188</v>
+        <v>7094057</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3200,7 +3205,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3210,12 +3215,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på stor kjolgran 7 m fr grusvägen.</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -786,53 +786,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125689348</v>
+        <v>125666987</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493404</v>
+        <v>493310</v>
       </c>
       <c r="R3" t="n">
-        <v>7094076</v>
+        <v>7094122</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -859,27 +856,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125683525</v>
+        <v>125689348</v>
       </c>
       <c r="B4" t="n">
         <v>57656</v>
@@ -935,21 +932,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493611</v>
+        <v>493404</v>
       </c>
       <c r="R4" t="n">
-        <v>7094209</v>
+        <v>7094076</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,50 +1023,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125666987</v>
+        <v>125683525</v>
       </c>
       <c r="B5" t="n">
-        <v>98373</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493310</v>
+        <v>493611</v>
       </c>
       <c r="R5" t="n">
-        <v>7094122</v>
+        <v>7094209</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,27 +1093,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2659,7 +2659,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125684220</v>
+        <v>125689294</v>
       </c>
       <c r="B19" t="n">
         <v>57656</v>
@@ -2688,24 +2688,21 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493495</v>
+        <v>493420</v>
       </c>
       <c r="R19" t="n">
-        <v>7094188</v>
+        <v>7094057</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2737,7 +2734,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,12 +2744,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på stor kjolgran 7 m fr grusvägen.</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2779,7 +2771,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125665967</v>
+        <v>125664781</v>
       </c>
       <c r="B20" t="n">
         <v>57656</v>
@@ -2810,19 +2802,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493355</v>
+        <v>493440</v>
       </c>
       <c r="R20" t="n">
-        <v>7094221</v>
+        <v>7094193</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2854,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2864,12 +2856,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretå på gran.</t>
+          <t>Färska och äldre ringhack av tretå ppå stor gran ca 30 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2896,7 +2888,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125664781</v>
+        <v>125684220</v>
       </c>
       <c r="B21" t="n">
         <v>57656</v>
@@ -2925,21 +2917,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493440</v>
+        <v>493495</v>
       </c>
       <c r="R21" t="n">
-        <v>7094193</v>
+        <v>7094188</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2966,27 +2961,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack av tretå ppå stor gran ca 30 m fr grusvägen.</t>
+          <t>Färska ringhack på stor kjolgran 7 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3130,7 +3125,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125689294</v>
+        <v>125665967</v>
       </c>
       <c r="B23" t="n">
         <v>57656</v>
@@ -3170,10 +3165,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493420</v>
+        <v>493355</v>
       </c>
       <c r="R23" t="n">
-        <v>7094057</v>
+        <v>7094221</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3200,22 +3195,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretå på gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3242,7 +3242,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125686241</v>
+        <v>125684017</v>
       </c>
       <c r="B24" t="n">
         <v>57656</v>
@@ -3275,23 +3275,23 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>strandflyn, Jmt</t>
+          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493197</v>
+        <v>493640</v>
       </c>
       <c r="R24" t="n">
-        <v>7094155</v>
+        <v>7094153</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Svårt med täckning och rätt koordinater men halvvägs ner i branten. Äldre ringhack.</t>
+          <t>Färska ringhack ca 2 m upp på gran 5 m fr myren.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3362,7 +3362,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125684017</v>
+        <v>125686241</v>
       </c>
       <c r="B25" t="n">
         <v>57656</v>
@@ -3395,23 +3395,23 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
+          <t>strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493640</v>
+        <v>493197</v>
       </c>
       <c r="R25" t="n">
-        <v>7094153</v>
+        <v>7094155</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack ca 2 m upp på gran 5 m fr myren.</t>
+          <t>Svårt med täckning och rätt koordinater men halvvägs ner i branten. Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3482,50 +3482,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125684959</v>
+        <v>125667340</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493277</v>
+        <v>493359</v>
       </c>
       <c r="R26" t="n">
-        <v>7093987</v>
+        <v>7094123</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3552,27 +3552,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack på 2 granar bredvid varandra</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3599,7 +3599,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125684059</v>
+        <v>125684959</v>
       </c>
       <c r="B27" t="n">
         <v>57656</v>
@@ -3635,14 +3635,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493628</v>
+        <v>493277</v>
       </c>
       <c r="R27" t="n">
-        <v>7094137</v>
+        <v>7093987</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
+          <t>Äldre ringhack på 2 granar bredvid varandra</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3716,50 +3716,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125667340</v>
+        <v>125684059</v>
       </c>
       <c r="B28" t="n">
-        <v>98373</v>
+        <v>57656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493359</v>
+        <v>493628</v>
       </c>
       <c r="R28" t="n">
-        <v>7094123</v>
+        <v>7094137</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3786,27 +3786,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -786,50 +786,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125666987</v>
+        <v>125689348</v>
       </c>
       <c r="B3" t="n">
-        <v>98373</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493310</v>
+        <v>493404</v>
       </c>
       <c r="R3" t="n">
-        <v>7094122</v>
+        <v>7094076</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -856,27 +859,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125689348</v>
+        <v>125683525</v>
       </c>
       <c r="B4" t="n">
         <v>57656</v>
@@ -932,24 +935,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493404</v>
+        <v>493611</v>
       </c>
       <c r="R4" t="n">
-        <v>7094076</v>
+        <v>7094209</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,50 +1023,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125683525</v>
+        <v>125666987</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493611</v>
+        <v>493310</v>
       </c>
       <c r="R5" t="n">
-        <v>7094209</v>
+        <v>7094122</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,27 +1093,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125667690</v>
       </c>
       <c r="B2" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>125689348</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>125683525</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>125666987</v>
       </c>
       <c r="B5" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>125667149</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125667551</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>125666667</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>125683879</v>
       </c>
       <c r="B9" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>125667483</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>125666555</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>125665004</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>125666380</v>
       </c>
       <c r="B13" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>125667284</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>125683817</v>
       </c>
       <c r="B15" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2308,50 +2308,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125666898</v>
+        <v>125683946</v>
       </c>
       <c r="B16" t="n">
-        <v>98373</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493284</v>
+        <v>493609</v>
       </c>
       <c r="R16" t="n">
-        <v>7094122</v>
+        <v>7094192</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2378,27 +2378,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,10 +2425,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125665862</v>
+        <v>125666898</v>
       </c>
       <c r="B17" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493347</v>
+        <v>493284</v>
       </c>
       <c r="R17" t="n">
-        <v>7094199</v>
+        <v>7094122</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
+          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,50 +2542,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125683946</v>
+        <v>125665862</v>
       </c>
       <c r="B18" t="n">
-        <v>57656</v>
+        <v>98382</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493609</v>
+        <v>493347</v>
       </c>
       <c r="R18" t="n">
-        <v>7094192</v>
+        <v>7094199</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2612,27 +2612,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran.</t>
+          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125689294</v>
+        <v>125684993</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,19 +2690,19 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493420</v>
+        <v>493273</v>
       </c>
       <c r="R19" t="n">
-        <v>7094057</v>
+        <v>7093990</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2744,7 +2744,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack nere på granen. Färska ringhack högre upp. 2 m fr bäcken.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2771,10 +2776,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125664781</v>
+        <v>125665967</v>
       </c>
       <c r="B20" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,19 +2807,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493440</v>
+        <v>493355</v>
       </c>
       <c r="R20" t="n">
-        <v>7094193</v>
+        <v>7094221</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2846,7 +2851,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2856,12 +2861,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack av tretå ppå stor gran ca 30 m fr grusvägen.</t>
+          <t>Äldre ringhack av tretå på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2888,10 +2893,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125684220</v>
+        <v>125689294</v>
       </c>
       <c r="B21" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,24 +2922,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493495</v>
+        <v>493420</v>
       </c>
       <c r="R21" t="n">
-        <v>7094188</v>
+        <v>7094057</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2966,7 +2968,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2976,12 +2978,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på stor kjolgran 7 m fr grusvägen.</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3008,10 +3005,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125684993</v>
+        <v>125664781</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,14 +3041,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493273</v>
+        <v>493440</v>
       </c>
       <c r="R22" t="n">
-        <v>7093990</v>
+        <v>7094193</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3078,27 +3075,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre ringhack nere på granen. Färska ringhack högre upp. 2 m fr bäcken.</t>
+          <t>Färska och äldre ringhack av tretå ppå stor gran ca 30 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3125,10 +3122,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125665967</v>
+        <v>125684220</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3154,21 +3151,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493355</v>
+        <v>493495</v>
       </c>
       <c r="R23" t="n">
-        <v>7094221</v>
+        <v>7094188</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3195,27 +3195,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretå på gran.</t>
+          <t>Färska ringhack på stor kjolgran 7 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3242,10 +3242,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125684017</v>
+        <v>125686241</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3275,23 +3275,23 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
+          <t>strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493640</v>
+        <v>493197</v>
       </c>
       <c r="R24" t="n">
-        <v>7094153</v>
+        <v>7094155</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack ca 2 m upp på gran 5 m fr myren.</t>
+          <t>Svårt med täckning och rätt koordinater men halvvägs ner i branten. Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3362,10 +3362,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125686241</v>
+        <v>125684017</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3395,23 +3395,23 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>strandflyn, Jmt</t>
+          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493197</v>
+        <v>493640</v>
       </c>
       <c r="R25" t="n">
-        <v>7094155</v>
+        <v>7094153</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Svårt med täckning och rätt koordinater men halvvägs ner i branten. Äldre ringhack.</t>
+          <t>Färska ringhack ca 2 m upp på gran 5 m fr myren.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3485,7 +3485,7 @@
         <v>125667340</v>
       </c>
       <c r="B26" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>125684959</v>
       </c>
       <c r="B27" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>125684059</v>
       </c>
       <c r="B28" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>125667230</v>
       </c>
       <c r="B29" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125667690</v>
+        <v>62515025</v>
       </c>
       <c r="B2" t="n">
-        <v>91245</v>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Storåbränna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493388</v>
+        <v>493202</v>
       </c>
       <c r="R2" t="n">
-        <v>7094155</v>
+        <v>7093984</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>18:20</t>
+          <t>2016-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18:20</t>
+          <t>2016-08-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,29 +754,47 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Lisa Linck</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Lisa Linck</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Myrskyddsplaneinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125689348</v>
+        <v>125667149</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,24 +820,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493404</v>
+        <v>493333</v>
       </c>
       <c r="R3" t="n">
-        <v>7094076</v>
+        <v>7094118</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -859,27 +861,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre hackringar på gran bredvid myrkanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125683525</v>
+        <v>125667230</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,14 +944,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493611</v>
+        <v>493333</v>
       </c>
       <c r="R4" t="n">
-        <v>7094209</v>
+        <v>7094132</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -976,27 +978,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
+          <t>Äldre hackringar av tretå på gran bredvid myren. 2 hackade granar bredvid varandra.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,38 +1025,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125666987</v>
+        <v>125667284</v>
       </c>
       <c r="B5" t="n">
-        <v>98382</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1063,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493310</v>
+        <v>493342</v>
       </c>
       <c r="R5" t="n">
-        <v>7094122</v>
+        <v>7094110</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1098,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack av tretå på grov gran med garnlav i.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125667149</v>
+        <v>125684959</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,14 +1178,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493333</v>
+        <v>493277</v>
       </c>
       <c r="R6" t="n">
-        <v>7094118</v>
+        <v>7093987</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1210,27 +1212,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre hackringar på gran bredvid myrkanten.</t>
+          <t>Äldre ringhack på 2 granar bredvid varandra</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125667551</v>
+        <v>125684993</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,14 +1295,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Lerbäcken, Lerbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493416</v>
+        <v>493273</v>
       </c>
       <c r="R7" t="n">
-        <v>7094160</v>
+        <v>7093990</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1327,27 +1329,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Mycket färska ringhack av tretå. Rinnande kåda.</t>
+          <t>Äldre ringhack nere på granen. Färska ringhack högre upp. 2 m fr bäcken.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125666667</v>
+        <v>125689294</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1414,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493264</v>
+        <v>493420</v>
       </c>
       <c r="R8" t="n">
-        <v>7094138</v>
+        <v>7094057</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1444,27 +1446,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på äldre gran.</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125683879</v>
+        <v>125689348</v>
       </c>
       <c r="B9" t="n">
-        <v>91263</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,37 +1499,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493545</v>
+        <v>493404</v>
       </c>
       <c r="R9" t="n">
-        <v>7094176</v>
+        <v>7094076</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1564,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,12 +1576,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På död avbruten granstubbe ca 40 m fr grusvägen.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,7 +1590,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1607,38 +1608,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125667483</v>
+        <v>125666898</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>99140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1647,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493407</v>
+        <v>493284</v>
       </c>
       <c r="R10" t="n">
-        <v>7094143</v>
+        <v>7094122</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1682,7 +1683,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1692,12 +1693,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack i gammelgran med garnlav.</t>
+          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,38 +1725,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125666555</v>
+        <v>125666987</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>99140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1764,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493270</v>
+        <v>493310</v>
       </c>
       <c r="R11" t="n">
-        <v>7094164</v>
+        <v>7094122</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1799,7 +1800,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1809,12 +1810,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,50 +1842,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125665004</v>
+        <v>125667340</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>99140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493493</v>
+        <v>493359</v>
       </c>
       <c r="R12" t="n">
-        <v>7094191</v>
+        <v>7094123</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1916,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1926,12 +1927,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack av tretå på gammal kjolgran med garnlav i ca 30 m fr grusvägen.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,50 +1959,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125666380</v>
+        <v>125667690</v>
       </c>
       <c r="B13" t="n">
-        <v>98382</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493279</v>
+        <v>493388</v>
       </c>
       <c r="R13" t="n">
-        <v>7094150</v>
+        <v>7094155</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2033,7 +2032,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2043,12 +2042,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Blad men även blomställningar med knopp. Rikligt på en yta ca 3 kvadratmeter.</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,6 +2051,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2075,10 +2070,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125667284</v>
+        <v>125683817</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,39 +2081,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493342</v>
+        <v>493580</v>
       </c>
       <c r="R14" t="n">
-        <v>7094110</v>
+        <v>7094211</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2145,27 +2138,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretå på grov gran med garnlav i.</t>
+          <t>På nedbruten granlåga. 30 m fr vägen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,6 +2167,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2192,10 +2186,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125683817</v>
+        <v>125664781</v>
       </c>
       <c r="B15" t="n">
-        <v>91245</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2203,37 +2197,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493580</v>
+        <v>493440</v>
       </c>
       <c r="R15" t="n">
-        <v>7094211</v>
+        <v>7094193</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2260,27 +2256,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På nedbruten granlåga. 30 m fr vägen.</t>
+          <t>Färska och äldre ringhack av tretå ppå stor gran ca 30 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,7 +2285,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2308,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125683946</v>
+        <v>125665004</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2334,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2348,10 +2343,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493609</v>
+        <v>493493</v>
       </c>
       <c r="R16" t="n">
-        <v>7094192</v>
+        <v>7094191</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2378,27 +2373,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran.</t>
+          <t>Färska och äldre ringhack av tretå på gammal kjolgran med garnlav i ca 30 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,38 +2420,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125666898</v>
+        <v>125665967</v>
       </c>
       <c r="B17" t="n">
-        <v>98382</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2465,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493284</v>
+        <v>493355</v>
       </c>
       <c r="R17" t="n">
-        <v>7094122</v>
+        <v>7094221</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2500,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,12 +2505,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på en yta av ca 9 kvadratmeter.</t>
+          <t>Äldre ringhack av tretå på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,38 +2537,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125665862</v>
+        <v>125666555</v>
       </c>
       <c r="B18" t="n">
-        <v>98382</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2582,10 +2577,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493347</v>
+        <v>493270</v>
       </c>
       <c r="R18" t="n">
-        <v>7094199</v>
+        <v>7094164</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2617,7 +2612,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2627,12 +2622,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
+          <t>Färska ringhack längre upp på stammen i granen med kåda rinnande. Äldre hack runt hela granen i stort sett.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,10 +2654,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125684993</v>
+        <v>125666667</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,19 +2685,19 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Jmt</t>
+          <t>Strandflyn, Strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493273</v>
+        <v>493264</v>
       </c>
       <c r="R19" t="n">
-        <v>7093990</v>
+        <v>7094138</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2729,27 +2724,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack nere på granen. Färska ringhack högre upp. 2 m fr bäcken.</t>
+          <t>Äldre ringhack på äldre gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,10 +2771,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125665967</v>
+        <v>125667483</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493355</v>
+        <v>493407</v>
       </c>
       <c r="R20" t="n">
-        <v>7094221</v>
+        <v>7094143</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2851,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2861,12 +2856,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretå på gran.</t>
+          <t>Äldre ringhack i gammelgran med garnlav.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2893,10 +2888,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125689294</v>
+        <v>125667551</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2919,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2933,10 +2928,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493420</v>
+        <v>493416</v>
       </c>
       <c r="R21" t="n">
-        <v>7094057</v>
+        <v>7094160</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2963,22 +2958,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Mycket färska ringhack av tretå. Rinnande kåda.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3005,10 +3005,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125664781</v>
+        <v>125683161</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493440</v>
+        <v>493584</v>
       </c>
       <c r="R22" t="n">
-        <v>7094193</v>
+        <v>7094254</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3075,27 +3075,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack av tretå ppå stor gran ca 30 m fr grusvägen.</t>
+          <t>Färska ringhack på gran 10 m fr vägen.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3122,10 +3122,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125684220</v>
+        <v>125683525</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,24 +3151,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493495</v>
+        <v>493611</v>
       </c>
       <c r="R23" t="n">
-        <v>7094188</v>
+        <v>7094209</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3200,7 +3197,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3210,12 +3207,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack på stor kjolgran 7 m fr grusvägen.</t>
+          <t>Äldre ringhack på gran 5 m fr tjärnen.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3242,10 +3239,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125686241</v>
+        <v>125683946</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,27 +3268,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>strandflyn, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493197</v>
+        <v>493609</v>
       </c>
       <c r="R24" t="n">
-        <v>7094155</v>
+        <v>7094192</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3320,7 +3314,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3330,12 +3324,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Svårt med täckning och rätt koordinater men halvvägs ner i branten. Äldre ringhack.</t>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3365,7 +3359,7 @@
         <v>125684017</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3482,50 +3476,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125667340</v>
+        <v>125684059</v>
       </c>
       <c r="B26" t="n">
-        <v>98382</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Strandflyn, Strandflyn, Jmt</t>
+          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493359</v>
+        <v>493628</v>
       </c>
       <c r="R26" t="n">
-        <v>7094123</v>
+        <v>7094137</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3552,27 +3546,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3599,10 +3593,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125684959</v>
+        <v>125684220</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3628,21 +3622,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lerbäcken, Lerbäcken, Jmt</t>
+          <t>Matsäckmyren, Matsäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493277</v>
+        <v>493495</v>
       </c>
       <c r="R27" t="n">
-        <v>7093987</v>
+        <v>7094188</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3674,7 +3671,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3684,12 +3681,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på 2 granar bredvid varandra</t>
+          <t>Färska ringhack på stor kjolgran 7 m fr grusvägen.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3716,10 +3713,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125684059</v>
+        <v>125686241</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3745,24 +3742,27 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Plogåstjärnbäcken, Plogåstjärnbäcken, Jmt</t>
+          <t>strandflyn, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493628</v>
+        <v>493197</v>
       </c>
       <c r="R28" t="n">
-        <v>7094137</v>
+        <v>7094155</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stor kjolgran ca 10 m fr myren.</t>
+          <t>Svårt med täckning och rätt koordinater men halvvägs ner i branten. Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3833,38 +3833,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125667230</v>
+        <v>125665862</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>99140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493333</v>
+        <v>493347</v>
       </c>
       <c r="R29" t="n">
-        <v>7094132</v>
+        <v>7094199</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre hackringar av tretå på gran bredvid myren. 2 hackade granar bredvid varandra.</t>
+          <t>Rikligt med blad men även blomknoppar på en yta av ca 9 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3947,6 +3947,123 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125666380</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Strandflyn, Strandflyn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>493279</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7094150</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Blad men även blomställningar med knopp. Rikligt på en yta ca 3 kvadratmeter.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18940-2025 artfynd.xlsx
+++ b/artfynd/A 18940-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125667690</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125683817</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
           <t>Myrskyddsplaneinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62515025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125664781</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1249,6 +1274,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125665004</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1366,6 +1396,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125665967</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1483,6 +1518,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125666555</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125666667</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1717,6 +1762,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125667149</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1834,6 +1884,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125667230</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1951,6 +2006,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125667284</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2068,6 +2128,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125667483</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2185,6 +2250,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125667551</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2302,6 +2372,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125683161</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2419,6 +2494,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125683525</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2536,6 +2616,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125683946</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2656,6 +2741,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125684017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2773,6 +2863,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125684059</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2893,6 +2988,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125684220</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3010,6 +3110,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125684959</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3127,6 +3232,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125684993</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3247,6 +3357,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125686241</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3359,6 +3474,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125689294</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3479,6 +3599,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125689348</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3596,6 +3721,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125665862</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3713,6 +3843,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125666380</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3830,6 +3965,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125666898</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3947,6 +4087,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125666987</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4064,8 +4209,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125667340</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>